--- a/tests/reference_data/example_scenario.xlsx
+++ b/tests/reference_data/example_scenario.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\PythonProjects\aiphoria\tests\reference_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFBA6502-DB90-48BA-9CC5-C32797B2541B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681101D5-8E33-41F1-8726-194E7E814D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
+    <workbookView xWindow="-25635" yWindow="2265" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="11" r:id="rId1"/>
@@ -5382,6 +5382,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="145cc194-9bea-4db6-b116-a042a4529fcd" xsi:nil="true"/>
+    <Comment xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Asiakirja" ma:contentTypeID="0x010100806C55B750152A459818B636E97A41C3" ma:contentTypeVersion="19" ma:contentTypeDescription="Luo uusi asiakirja." ma:contentTypeScope="" ma:versionID="74fd9cb75cef04cf26a1ff9ddef01b4b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xmlns:ns3="145cc194-9bea-4db6-b116-a042a4529fcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="afbcbfdd38894bc2ff0644b00c8ec680" ns2:_="" ns3:_="">
     <xsd:import namespace="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
@@ -5644,28 +5665,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="145cc194-9bea-4db6-b116-a042a4529fcd" xsi:nil="true"/>
-    <Comment xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557FAA9C-B184-448F-B58D-00E4D46BDD72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="145cc194-9bea-4db6-b116-a042a4529fcd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60021C7-CA75-4673-96EA-55284BF81134}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5682,29 +5707,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557FAA9C-B184-448F-B58D-00E4D46BDD72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="145cc194-9bea-4db6-b116-a042a4529fcd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>